--- a/outputs/analysis/budget_recommendation.xlsx
+++ b/outputs/analysis/budget_recommendation.xlsx
@@ -499,10 +499,10 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>17273.495</v>
+        <v>34546.99</v>
       </c>
       <c r="C3">
-        <v>15000</v>
+        <v>30000</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/analysis/budget_recommendation.xlsx
+++ b/outputs/analysis/budget_recommendation.xlsx
@@ -7,42 +7,108 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenario 1 - Status Quo" sheetId="1" r:id="rId1"/>
-    <sheet name="Scenario 2 - ROI Optimized" sheetId="2" r:id="rId2"/>
-    <sheet name="Scenario 3 - Growth Mode" sheetId="3" r:id="rId3"/>
+    <sheet name="Tracked Spend Evidence" sheetId="1" r:id="rId1"/>
+    <sheet name="Measurement Scenarios" sheetId="2" r:id="rId2"/>
+    <sheet name="Assumptions" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
+  <si>
+    <t>channel_category</t>
+  </si>
+  <si>
+    <t>channel_spend</t>
+  </si>
+  <si>
+    <t>deal_count</t>
+  </si>
+  <si>
+    <t>resolved_count</t>
+  </si>
+  <si>
+    <t>won_count</t>
+  </si>
+  <si>
+    <t>total_pipeline</t>
+  </si>
+  <si>
+    <t>won_pipeline</t>
+  </si>
+  <si>
+    <t>pipeline_roi</t>
+  </si>
+  <si>
+    <t>revenue_roi</t>
+  </si>
+  <si>
+    <t>evidence_status</t>
+  </si>
+  <si>
+    <t>6sense_display</t>
+  </si>
+  <si>
+    <t>linkedin</t>
+  </si>
+  <si>
+    <t>Insufficient outcome evidence</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
   <si>
     <t>Channel</t>
   </si>
   <si>
-    <t>Current Spend ($)</t>
-  </si>
-  <si>
-    <t>Pipeline ($)</t>
-  </si>
-  <si>
-    <t>Pipeline ROI (x)</t>
-  </si>
-  <si>
-    <t>6sense_display</t>
-  </si>
-  <si>
-    <t>linkedin</t>
-  </si>
-  <si>
-    <t>Recommended Spend ($)</t>
-  </si>
-  <si>
-    <t>Projected Pipeline ($)</t>
-  </si>
-  <si>
-    <t>Aggressive Spend ($)</t>
+    <t>Active Spend ($)</t>
+  </si>
+  <si>
+    <t>Holdout Reserve ($)</t>
+  </si>
+  <si>
+    <t>Experiment Pool ($)</t>
+  </si>
+  <si>
+    <t>Total Budget ($)</t>
+  </si>
+  <si>
+    <t>Evidence Status</t>
+  </si>
+  <si>
+    <t>Status Quo</t>
+  </si>
+  <si>
+    <t>10% Holdout</t>
+  </si>
+  <si>
+    <t>Measurement First</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Budget neutrality</t>
+  </si>
+  <si>
+    <t>No pipeline forecast</t>
+  </si>
+  <si>
+    <t>Decision gate</t>
+  </si>
+  <si>
+    <t>Every scenario preserves the current tracked-spend total.</t>
+  </si>
+  <si>
+    <t>Historical ROI is not extrapolated because only two channels have spend and one has a single opportunity.</t>
+  </si>
+  <si>
+    <t>Scale only after a pre-registered holdout shows incremental opportunity or pipeline lift with acceptable win-rate quality.</t>
   </si>
 </sst>
 </file>
@@ -374,10 +440,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -390,33 +456,87 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>1186809.5</v>
       </c>
       <c r="C2">
+        <v>90</v>
+      </c>
+      <c r="D2">
+        <v>86</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>89016</v>
       </c>
-      <c r="D2">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>0.08</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>34546.99</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>30000</v>
       </c>
-      <c r="D3">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <v>0.87</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -426,40 +546,168 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
-        <v>1234281.88</v>
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>92576.64000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>1186809.5</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1186809.5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>35928.8696</v>
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>31200</v>
+        <v>34546.99</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>34546.99</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>1068128.55</v>
+      </c>
+      <c r="D4">
+        <v>118680.95</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1186809.5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>31092.291</v>
+      </c>
+      <c r="D5">
+        <v>3454.699</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>34546.99</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>949447.6000000001</v>
+      </c>
+      <c r="D6">
+        <v>118680.95</v>
+      </c>
+      <c r="E6">
+        <v>118680.95</v>
+      </c>
+      <c r="F6">
+        <v>1186809.5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>27637.592</v>
+      </c>
+      <c r="D7">
+        <v>3454.699</v>
+      </c>
+      <c r="E7">
+        <v>3454.699</v>
+      </c>
+      <c r="F7">
+        <v>34546.99</v>
+      </c>
+      <c r="G7" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -469,40 +717,39 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
-        <v>1186809.5</v>
-      </c>
-      <c r="C2">
-        <v>89016</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>34546.99</v>
-      </c>
-      <c r="C3">
-        <v>30000</v>
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
